--- a/SuppXLS/Scen_ELCHEAT_20_50_BOUND.xlsx
+++ b/SuppXLS/Scen_ELCHEAT_20_50_BOUND.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/meselu_tegenie_mellaku_nmbu_no/Documents/Documents/GitHub/MANU2025/SuppXLS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{C4DCE02A-42CF-45AF-B295-C69FD6AF9674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{440343A7-70CC-44A9-8876-C3FD87F16055}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BEB55D-33A9-4FA1-8CA3-6C4FF6B67B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELCHEAT_BND" sheetId="2" r:id="rId1"/>
@@ -168,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,6 +212,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -259,7 +266,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -276,6 +283,8 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -293,10 +302,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -587,26 +592,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.26953125" customWidth="1"/>
-    <col min="5" max="9" width="8.7265625" customWidth="1"/>
-    <col min="10" max="11" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.21875" customWidth="1"/>
+    <col min="5" max="9" width="8.77734375" customWidth="1"/>
+    <col min="10" max="11" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -619,7 +624,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -666,7 +671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>25</v>
       </c>
@@ -687,7 +692,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>25</v>
       </c>
@@ -708,17 +713,17 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>18</v>
       </c>
@@ -750,60 +755,62 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" t="s">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="11">
         <v>3256.4</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="11">
         <v>4273.3500000000004</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="11">
         <v>6721.82</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="11">
         <v>10573.18</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="11">
         <v>16631.23</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="11">
         <v>26160.32</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="11">
         <v>41149.22</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
